--- a/Hoàng/Gói 1,2,3/GÓI 1,2,3.xlsx
+++ b/Hoàng/Gói 1,2,3/GÓI 1,2,3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA-TN\Hoàng\Gói 1,2,3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\Gói 1,2,3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC7729A-D148-44CE-8F4D-473198E8D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE7E5D7-7873-412F-B4BE-28BB7CBBC8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GÓI 1tr6" sheetId="9" r:id="rId1"/>
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="128">
   <si>
     <t xml:space="preserve">CÔNG TY CỔ PHẦN BỆNH VIỆN THIỆN NHÂN ĐÀ NẴNG 
 Số 276-278-280 Đống Đa - P Thanh Bình -Thành Phố Đà Nẵng 
@@ -612,6 +612,9 @@
   </si>
   <si>
     <t>Lưu ý</t>
+  </si>
+  <si>
+    <t>. Ms Sương ( PGĐ.KD) : 0935 345 693</t>
   </si>
 </sst>
 </file>
@@ -619,21 +622,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1073,9 +1076,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1278,7 +1281,7 @@
     <xf numFmtId="3" fontId="13" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1315,6 +1318,21 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1327,200 +1345,182 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2702,72 +2702,72 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="7" width="17.25" style="68" customWidth="1"/>
-    <col min="8" max="8" width="28.25" style="69" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="19" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="6.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="7" width="17.28515625" style="68" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="69" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="19" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="147"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="118"/>
-    </row>
-    <row r="2" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="116"/>
+    </row>
+    <row r="2" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="118"/>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="116"/>
+    </row>
+    <row r="3" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="118"/>
-    </row>
-    <row r="4" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="116"/>
+    </row>
+    <row r="4" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="118"/>
-    </row>
-    <row r="5" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="116"/>
+    </row>
+    <row r="5" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="121"/>
-    </row>
-    <row r="6" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="119"/>
+    </row>
+    <row r="6" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -2777,24 +2777,24 @@
       <c r="G6" s="7"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:13" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:13" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="122"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -2809,184 +2809,184 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="125"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="128"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="149"/>
-      <c r="B11" s="150"/>
-      <c r="C11" s="150"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="151"/>
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="129"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="131"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="134" t="s">
+    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="134" t="s">
+      <c r="B12" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134" t="s">
+      <c r="C12" s="96"/>
+      <c r="D12" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="145" t="s">
+      <c r="E12" s="102" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="152" t="s">
+      <c r="F12" s="103" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="152"/>
-      <c r="H12" s="146" t="s">
+      <c r="G12" s="103"/>
+      <c r="H12" s="91" t="s">
         <v>7</v>
       </c>
       <c r="I12" s="27"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="134"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="145"/>
+    <row r="13" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="96"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="102"/>
       <c r="F13" s="21" t="s">
         <v>95</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="146"/>
-      <c r="I13" s="148"/>
-    </row>
-    <row r="14" spans="1:13" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+      <c r="H13" s="91"/>
+      <c r="I13" s="87"/>
+    </row>
+    <row r="14" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
-      <c r="G14" s="142">
+      <c r="G14" s="97">
         <v>200000</v>
       </c>
       <c r="H14" s="107"/>
       <c r="I14" s="25"/>
     </row>
-    <row r="15" spans="1:13" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
       <c r="H15" s="108"/>
       <c r="I15" s="25"/>
     </row>
-    <row r="16" spans="1:13" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:13" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
       <c r="H16" s="108"/>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
       <c r="H17" s="108"/>
       <c r="I17" s="27"/>
     </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
       <c r="H18" s="108"/>
       <c r="I18" s="27"/>
     </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
       <c r="H19" s="109"/>
       <c r="I19" s="27"/>
     </row>
-    <row r="20" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -3012,7 +3012,7 @@
       <c r="H20" s="33"/>
       <c r="I20" s="27"/>
     </row>
-    <row r="21" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -3038,7 +3038,7 @@
       <c r="H21" s="33"/>
       <c r="I21" s="27"/>
     </row>
-    <row r="22" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -3064,7 +3064,7 @@
       <c r="H22" s="33"/>
       <c r="I22" s="27"/>
     </row>
-    <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -3090,7 +3090,7 @@
       <c r="H23" s="33"/>
       <c r="I23" s="27"/>
     </row>
-    <row r="24" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -3104,21 +3104,21 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="111">
+      <c r="G24" s="100">
         <v>60000</v>
       </c>
-      <c r="H24" s="113" t="s">
+      <c r="H24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="27"/>
     </row>
-    <row r="25" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -3130,13 +3130,13 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="112"/>
       <c r="I25" s="27"/>
     </row>
-    <row r="26" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -3162,12 +3162,12 @@
       <c r="H26" s="33"/>
       <c r="I26" s="27"/>
     </row>
-    <row r="27" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="H27" s="27"/>
     </row>
-    <row r="28" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="H28" s="27"/>
     </row>
-    <row r="29" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
         <v>11</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>101</v>
       </c>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="H29" s="27"/>
     </row>
-    <row r="30" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>56</v>
       </c>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="H30" s="27"/>
     </row>
-    <row r="31" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
@@ -3271,11 +3271,11 @@
       <c r="E31" s="45">
         <v>79000</v>
       </c>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
       <c r="H31" s="27"/>
     </row>
-    <row r="32" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
@@ -3292,14 +3292,14 @@
       <c r="E32" s="42">
         <v>41000</v>
       </c>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
       <c r="H32" s="43" t="s">
         <v>50</v>
       </c>
       <c r="I32" s="27"/>
     </row>
-    <row r="33" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
@@ -3323,7 +3323,7 @@
       <c r="H33" s="33"/>
       <c r="I33" s="27"/>
     </row>
-    <row r="34" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
@@ -3338,12 +3338,12 @@
       <c r="E34" s="36">
         <v>250000</v>
       </c>
-      <c r="F34" s="155"/>
-      <c r="G34" s="154"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="89"/>
       <c r="H34" s="33"/>
       <c r="I34" s="27"/>
     </row>
-    <row r="35" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
@@ -3358,12 +3358,12 @@
       <c r="E35" s="41">
         <v>230000</v>
       </c>
-      <c r="F35" s="154"/>
-      <c r="G35" s="154"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
       <c r="H35" s="33"/>
       <c r="I35" s="27"/>
     </row>
-    <row r="36" spans="1:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
@@ -3387,13 +3387,13 @@
       <c r="H36" s="33"/>
       <c r="I36" s="27"/>
     </row>
-    <row r="37" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="93" t="s">
+    <row r="37" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="95"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="106"/>
       <c r="E37" s="21">
         <f>SUM(E14:E35)</f>
         <v>1600000</v>
@@ -3409,7 +3409,7 @@
       <c r="H37" s="38"/>
       <c r="I37" s="27"/>
     </row>
-    <row r="38" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="50"/>
       <c r="B38" s="51"/>
       <c r="C38" s="50"/>
@@ -3419,7 +3419,7 @@
       <c r="G38" s="52"/>
       <c r="H38" s="53"/>
     </row>
-    <row r="39" spans="1:9" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="62" t="s">
         <v>126</v>
       </c>
@@ -3431,67 +3431,67 @@
       <c r="G39" s="64"/>
       <c r="H39" s="65"/>
     </row>
-    <row r="40" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="56"/>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-    </row>
-    <row r="41" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+    </row>
+    <row r="41" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="56"/>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="88"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="88"/>
-      <c r="H41" s="88"/>
-    </row>
-    <row r="42" spans="1:9" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+    </row>
+    <row r="42" spans="1:9" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="57"/>
-      <c r="B42" s="88" t="s">
+      <c r="B42" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="88"/>
-      <c r="D42" s="88"/>
-      <c r="E42" s="88"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="88"/>
-      <c r="H42" s="88"/>
-    </row>
-    <row r="43" spans="1:9" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="93"/>
+      <c r="D42" s="93"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="93"/>
+      <c r="G42" s="93"/>
+      <c r="H42" s="93"/>
+    </row>
+    <row r="43" spans="1:9" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="59"/>
-      <c r="B43" s="87" t="s">
+      <c r="B43" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="87"/>
-      <c r="D43" s="87"/>
-      <c r="E43" s="87"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="87"/>
-    </row>
-    <row r="44" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="92"/>
+      <c r="G43" s="92"/>
+      <c r="H43" s="92"/>
+    </row>
+    <row r="44" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="54"/>
-      <c r="B44" s="88" t="s">
+      <c r="B44" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="88"/>
-    </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+    </row>
+    <row r="45" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="54"/>
       <c r="B45" s="57" t="s">
         <v>88</v>
@@ -3503,7 +3503,7 @@
       <c r="G45" s="7"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="54"/>
       <c r="B46" s="57" t="s">
         <v>89</v>
@@ -3515,7 +3515,7 @@
       <c r="G46" s="7"/>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="1:9" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="62" t="s">
         <v>90</v>
       </c>
@@ -3527,12 +3527,12 @@
       <c r="G47" s="64"/>
       <c r="H47" s="65"/>
     </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="54"/>
-      <c r="B48" s="89" t="s">
+      <c r="B48" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C48" s="90" t="s">
+      <c r="C48" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D48" s="61"/>
@@ -3541,7 +3541,7 @@
       <c r="G48" s="10"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="54"/>
       <c r="B49" s="5" t="s">
         <v>93</v>
@@ -3553,7 +3553,7 @@
       <c r="G49" s="10"/>
       <c r="H49" s="5"/>
     </row>
-    <row r="50" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="54"/>
       <c r="B50" s="5" t="s">
         <v>94</v>
@@ -3567,6 +3567,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D1:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A10:H11"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="G14:G19"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="B27:B30"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B44:H44"/>
@@ -3583,38 +3597,22 @@
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="H14:H19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="D1:H5"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="A10:H11"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="F14:F19"/>
-    <mergeCell ref="G14:G19"/>
   </mergeCells>
-  <conditionalFormatting sqref="C49:C1048576 C1:C11 C32:C38 C14:C26 C40:C47">
-    <cfRule type="duplicateValues" dxfId="59" priority="5"/>
+  <conditionalFormatting sqref="C27:C31">
+    <cfRule type="duplicateValues" dxfId="59" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:C38 C1:C11 C14:C26 C40:C1048576">
     <cfRule type="duplicateValues" dxfId="58" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C31">
-    <cfRule type="duplicateValues" dxfId="57" priority="6"/>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C49:C1048576 C1:C11 C32:C38 C14:C26 C40:C47">
+    <cfRule type="duplicateValues" dxfId="55" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="163" man="1"/>
   </colBreaks>
@@ -3628,67 +3626,68 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="6" width="13.4140625" style="68" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="69" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="7.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="17" style="68" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-    </row>
-    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-    </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -3697,23 +3696,23 @@
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -3727,52 +3726,52 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -3781,14 +3780,14 @@
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:12" ht="33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="134"/>
+      <c r="C13" s="96"/>
       <c r="D13" s="20" t="s">
         <v>6</v>
       </c>
@@ -3803,90 +3802,90 @@
       </c>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+    <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
       <c r="G14" s="107"/>
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="108"/>
       <c r="H15" s="25"/>
     </row>
-    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="108"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="108"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="108"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="109"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -3909,7 +3908,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -3932,7 +3931,7 @@
       <c r="G21" s="33"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -3955,7 +3954,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -3978,7 +3977,7 @@
       <c r="G23" s="33"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -3992,18 +3991,18 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -4015,12 +4014,12 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -4043,12 +4042,12 @@
       <c r="G26" s="33"/>
       <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -4065,12 +4064,12 @@
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -4085,12 +4084,12 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
         <v>11</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>101</v>
       </c>
@@ -4105,12 +4104,12 @@
       </c>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>56</v>
       </c>
@@ -4125,7 +4124,7 @@
       </c>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
@@ -4146,7 +4145,7 @@
       <c r="G31" s="33"/>
       <c r="H31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
@@ -4167,13 +4166,13 @@
       <c r="G32" s="33"/>
       <c r="H32" s="27"/>
     </row>
-    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="93" t="s">
+    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="106"/>
       <c r="E33" s="21">
         <f>SUM(E14:E32)</f>
         <v>1000000</v>
@@ -4185,7 +4184,7 @@
       <c r="G33" s="38"/>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="50"/>
       <c r="B34" s="51"/>
       <c r="C34" s="50"/>
@@ -4194,73 +4193,73 @@
       <c r="F34" s="52"/>
       <c r="G34" s="53"/>
     </row>
-    <row r="35" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="96" t="s">
+    <row r="35" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="144" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="144"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="54"/>
     </row>
-    <row r="36" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
-      <c r="B36" s="88" t="s">
+      <c r="B36" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="88"/>
-      <c r="D36" s="88"/>
-      <c r="E36" s="88"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88"/>
-    </row>
-    <row r="37" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+    </row>
+    <row r="37" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
-      <c r="B37" s="88" t="s">
+      <c r="B37" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-    </row>
-    <row r="38" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
+      <c r="F37" s="93"/>
+      <c r="G37" s="93"/>
+    </row>
+    <row r="38" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="57"/>
-      <c r="B38" s="88" t="s">
+      <c r="B38" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
-    </row>
-    <row r="39" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="93"/>
+    </row>
+    <row r="39" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="59"/>
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
-      <c r="G39" s="87"/>
-    </row>
-    <row r="40" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+    </row>
+    <row r="40" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="54"/>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-    </row>
-    <row r="41" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
+    </row>
+    <row r="41" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="54"/>
       <c r="B41" s="57" t="s">
         <v>88</v>
@@ -4271,7 +4270,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="54"/>
       <c r="B42" s="57" t="s">
         <v>89</v>
@@ -4282,7 +4281,7 @@
       <c r="F42" s="7"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:8" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="62" t="s">
         <v>90</v>
       </c>
@@ -4293,12 +4292,12 @@
       <c r="F43" s="64"/>
       <c r="G43" s="65"/>
     </row>
-    <row r="44" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="54"/>
-      <c r="B44" s="89" t="s">
+      <c r="B44" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="90" t="s">
+      <c r="C44" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D44" s="61"/>
@@ -4306,10 +4305,10 @@
       <c r="F44" s="10"/>
       <c r="G44" s="5"/>
     </row>
-    <row r="45" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="54"/>
       <c r="B45" s="5" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="61"/>
@@ -4317,7 +4316,7 @@
       <c r="F45" s="10"/>
       <c r="G45" s="5"/>
     </row>
-    <row r="46" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="54"/>
       <c r="B46" s="5" t="s">
         <v>94</v>
@@ -4330,14 +4329,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="F14:F19"/>
-    <mergeCell ref="G14:G19"/>
-    <mergeCell ref="D1:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A10:G11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E14:E19"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="A14:A19"/>
@@ -4354,15 +4345,23 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="G14:G19"/>
+    <mergeCell ref="D1:G5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E14:E19"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="56" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="163" man="1"/>
   </colBreaks>
@@ -4376,67 +4375,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L71"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="6" width="17.25" style="68" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="69" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="6.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="6" width="17.28515625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-    </row>
-    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-    </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4445,23 +4444,23 @@
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -4475,52 +4474,52 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -4529,14 +4528,14 @@
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="134"/>
+      <c r="C13" s="96"/>
       <c r="D13" s="20" t="s">
         <v>6</v>
       </c>
@@ -4551,90 +4550,90 @@
       </c>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+    <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
       <c r="G14" s="107"/>
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="108"/>
       <c r="H15" s="25"/>
     </row>
-    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="108"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="108"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="108"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="109"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -4657,7 +4656,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -4680,7 +4679,7 @@
       <c r="G21" s="33"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -4703,7 +4702,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -4726,7 +4725,7 @@
       <c r="G23" s="33"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -4740,18 +4739,18 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -4763,12 +4762,12 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -4791,12 +4790,12 @@
       <c r="G26" s="33"/>
       <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -4813,12 +4812,12 @@
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -4833,12 +4832,12 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C29:C$34))</f>
         <v>6</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>122</v>
       </c>
@@ -4853,12 +4852,12 @@
       </c>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>101</v>
       </c>
@@ -4873,12 +4872,12 @@
       </c>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
       </c>
-      <c r="B31" s="115"/>
+      <c r="B31" s="113"/>
       <c r="C31" s="34" t="s">
         <v>56</v>
       </c>
@@ -4893,7 +4892,7 @@
       </c>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
@@ -4913,12 +4912,12 @@
       </c>
       <c r="G32" s="27"/>
     </row>
-    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
       </c>
-      <c r="B33" s="97" t="s">
+      <c r="B33" s="135" t="s">
         <v>33</v>
       </c>
       <c r="C33" s="34" t="s">
@@ -4936,12 +4935,12 @@
       </c>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
       </c>
-      <c r="B34" s="98"/>
+      <c r="B34" s="137"/>
       <c r="C34" s="34" t="s">
         <v>51</v>
       </c>
@@ -4957,7 +4956,7 @@
       </c>
       <c r="H34" s="27"/>
     </row>
-    <row r="35" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
@@ -4978,7 +4977,7 @@
       <c r="G35" s="33"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
@@ -4999,7 +4998,7 @@
       <c r="G36" s="33"/>
       <c r="H36" s="27"/>
     </row>
-    <row r="37" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <f>IF(LEN(C37)=0,"",COUNTA($C$14:C37))</f>
         <v>19</v>
@@ -5019,7 +5018,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
     </row>
-    <row r="38" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <f>IF(LEN(C38)=0,"",COUNTA($C$14:C38))</f>
         <v>20</v>
@@ -5037,7 +5036,7 @@
       <c r="F38" s="72"/>
       <c r="G38" s="27"/>
     </row>
-    <row r="39" spans="1:10" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <f>IF(LEN(C39)=0,"",COUNTA($C$35:C39))</f>
         <v>5</v>
@@ -5057,7 +5056,7 @@
       </c>
       <c r="G39" s="39"/>
     </row>
-    <row r="40" spans="1:10" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
         <f>IF(LEN(C40)=0,"",COUNTA($C$35:C46))</f>
         <v>12</v>
@@ -5077,7 +5076,7 @@
       </c>
       <c r="G40" s="39"/>
     </row>
-    <row r="41" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
         <f>IF(LEN(C41)=0,"",COUNTA($C$14:C41))</f>
         <v>23</v>
@@ -5100,7 +5099,7 @@
       <c r="G41" s="33"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
         <f>IF(LEN(C42)=0,"",COUNTA($C$35:C42))</f>
         <v>8</v>
@@ -5122,12 +5121,12 @@
       </c>
       <c r="G42" s="27"/>
     </row>
-    <row r="43" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="28">
         <f>IF(LEN(C43)=0,"",COUNTA($C$35:C43))</f>
         <v>9</v>
       </c>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="145" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="24" t="s">
@@ -5142,16 +5141,16 @@
       <c r="F43" s="45">
         <v>30000</v>
       </c>
-      <c r="G43" s="100" t="s">
+      <c r="G43" s="146" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="40" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" s="40" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="28">
         <f>IF(LEN(C44)=0,"",COUNTA($C$35:C44))</f>
         <v>10</v>
       </c>
-      <c r="B44" s="99"/>
+      <c r="B44" s="145"/>
       <c r="C44" s="24" t="s">
         <v>108</v>
       </c>
@@ -5164,20 +5163,20 @@
       <c r="F44" s="45">
         <v>20000</v>
       </c>
-      <c r="G44" s="101"/>
-    </row>
-    <row r="45" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G44" s="147"/>
+    </row>
+    <row r="45" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
         <f>IF(LEN(C45)=0,"",COUNTA($C$14:C45))</f>
         <v>27</v>
       </c>
-      <c r="B45" s="91" t="s">
+      <c r="B45" s="148" t="s">
         <v>62</v>
       </c>
       <c r="C45" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="103" t="s">
+      <c r="D45" s="150" t="s">
         <v>64</v>
       </c>
       <c r="E45" s="32">
@@ -5186,31 +5185,31 @@
       <c r="F45" s="32">
         <v>137000</v>
       </c>
-      <c r="G45" s="105" t="s">
+      <c r="G45" s="152" t="s">
         <v>65</v>
       </c>
       <c r="H45" s="39"/>
     </row>
-    <row r="46" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
         <f>IF(LEN(C46)=0,"",COUNTA($C$14:C46))</f>
         <v>28</v>
       </c>
-      <c r="B46" s="102"/>
+      <c r="B46" s="149"/>
       <c r="C46" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="104"/>
+      <c r="D46" s="151"/>
       <c r="E46" s="32">
         <v>137000</v>
       </c>
       <c r="F46" s="32">
         <v>137000</v>
       </c>
-      <c r="G46" s="106"/>
+      <c r="G46" s="153"/>
       <c r="H46" s="39"/>
     </row>
-    <row r="47" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A47" s="28">
         <f>IF(LEN(C47)=0,"",COUNTA($C$14:C47))</f>
         <v>29</v>
@@ -5231,7 +5230,7 @@
       <c r="G47" s="33"/>
       <c r="H47" s="27"/>
     </row>
-    <row r="48" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A48" s="28">
         <f>IF(LEN(C48)=0,"",COUNTA($C$14:C48))</f>
         <v>30</v>
@@ -5250,7 +5249,7 @@
       <c r="G48" s="33"/>
       <c r="H48" s="27"/>
     </row>
-    <row r="49" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="28">
         <f>IF(LEN(C49)=0,"",COUNTA($C$14:C49))</f>
         <v>31</v>
@@ -5271,7 +5270,7 @@
       <c r="G49" s="33"/>
       <c r="H49" s="27"/>
     </row>
-    <row r="50" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A50" s="28">
         <f>IF(LEN(C50)=0,"",COUNTA($C$35:C50))</f>
         <v>16</v>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="G50" s="27"/>
     </row>
-    <row r="51" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A51" s="28">
         <f>IF(LEN(C51)=0,"",COUNTA($C$14:C51))</f>
         <v>33</v>
@@ -5310,7 +5309,7 @@
       <c r="G51" s="33"/>
       <c r="H51" s="27"/>
     </row>
-    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="28">
         <f>IF(LEN(C52)=0,"",COUNTA($C$14:C52))</f>
         <v>34</v>
@@ -5329,7 +5328,7 @@
       <c r="G52" s="33"/>
       <c r="H52" s="27"/>
     </row>
-    <row r="53" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A53" s="28">
         <f>IF(LEN(C53)=0,"",COUNTA($C$14:C53))</f>
         <v>35</v>
@@ -5348,7 +5347,7 @@
       <c r="G53" s="33"/>
       <c r="H53" s="27"/>
     </row>
-    <row r="54" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A54" s="28">
         <f>IF(LEN(C54)=0,"",COUNTA($C$35:C54))</f>
         <v>20</v>
@@ -5368,12 +5367,12 @@
       </c>
       <c r="G54" s="27"/>
     </row>
-    <row r="55" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A55" s="28">
         <f>IF(LEN(C55)=0,"",COUNTA($C$14:C55))</f>
         <v>37</v>
       </c>
-      <c r="B55" s="91" t="s">
+      <c r="B55" s="148" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="24" t="s">
@@ -5391,12 +5390,12 @@
       <c r="G55" s="33"/>
       <c r="H55" s="27"/>
     </row>
-    <row r="56" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A56" s="28">
         <f>IF(LEN(C56)=0,"",COUNTA($C$14:C56))</f>
         <v>38</v>
       </c>
-      <c r="B56" s="92"/>
+      <c r="B56" s="154"/>
       <c r="C56" s="24" t="s">
         <v>76</v>
       </c>
@@ -5412,7 +5411,7 @@
       <c r="G56" s="33"/>
       <c r="H56" s="27"/>
     </row>
-    <row r="57" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="28">
         <f>IF(LEN(C57)=0,"",COUNTA($C$14:C57))</f>
         <v>39</v>
@@ -5433,13 +5432,13 @@
       <c r="G57" s="33"/>
       <c r="H57" s="27"/>
     </row>
-    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="93" t="s">
+    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="94"/>
-      <c r="C58" s="94"/>
-      <c r="D58" s="95"/>
+      <c r="B58" s="105"/>
+      <c r="C58" s="105"/>
+      <c r="D58" s="106"/>
       <c r="E58" s="21">
         <f>SUM(E14:E57)</f>
         <v>3981000</v>
@@ -5451,7 +5450,7 @@
       <c r="G58" s="38"/>
       <c r="H58" s="27"/>
     </row>
-    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="50"/>
       <c r="B59" s="51"/>
       <c r="C59" s="50"/>
@@ -5460,73 +5459,73 @@
       <c r="F59" s="52"/>
       <c r="G59" s="53"/>
     </row>
-    <row r="60" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="96" t="s">
+    <row r="60" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="B60" s="96"/>
-      <c r="C60" s="96"/>
-      <c r="D60" s="96"/>
+      <c r="B60" s="144"/>
+      <c r="C60" s="144"/>
+      <c r="D60" s="144"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="54"/>
     </row>
-    <row r="61" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="56"/>
-      <c r="B61" s="88" t="s">
+      <c r="B61" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="88"/>
-      <c r="D61" s="88"/>
-      <c r="E61" s="88"/>
-      <c r="F61" s="88"/>
-      <c r="G61" s="88"/>
-    </row>
-    <row r="62" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C61" s="93"/>
+      <c r="D61" s="93"/>
+      <c r="E61" s="93"/>
+      <c r="F61" s="93"/>
+      <c r="G61" s="93"/>
+    </row>
+    <row r="62" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="56"/>
-      <c r="B62" s="88" t="s">
+      <c r="B62" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="88"/>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
-    </row>
-    <row r="63" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="93"/>
+      <c r="D62" s="93"/>
+      <c r="E62" s="93"/>
+      <c r="F62" s="93"/>
+      <c r="G62" s="93"/>
+    </row>
+    <row r="63" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="57"/>
-      <c r="B63" s="88" t="s">
+      <c r="B63" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="88"/>
-      <c r="D63" s="88"/>
-      <c r="E63" s="88"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="88"/>
-    </row>
-    <row r="64" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="93"/>
+      <c r="D63" s="93"/>
+      <c r="E63" s="93"/>
+      <c r="F63" s="93"/>
+      <c r="G63" s="93"/>
+    </row>
+    <row r="64" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="59"/>
-      <c r="B64" s="87" t="s">
+      <c r="B64" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="87"/>
-      <c r="D64" s="87"/>
-      <c r="E64" s="87"/>
-      <c r="F64" s="87"/>
-      <c r="G64" s="87"/>
-    </row>
-    <row r="65" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+    </row>
+    <row r="65" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="54"/>
-      <c r="B65" s="88" t="s">
+      <c r="B65" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="88"/>
-      <c r="D65" s="88"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="88"/>
-      <c r="G65" s="88"/>
-    </row>
-    <row r="66" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C65" s="93"/>
+      <c r="D65" s="93"/>
+      <c r="E65" s="93"/>
+      <c r="F65" s="93"/>
+      <c r="G65" s="93"/>
+    </row>
+    <row r="66" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="54"/>
       <c r="B66" s="57" t="s">
         <v>88</v>
@@ -5537,7 +5536,7 @@
       <c r="F66" s="7"/>
       <c r="G66" s="5"/>
     </row>
-    <row r="67" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A67" s="54"/>
       <c r="B67" s="57" t="s">
         <v>89</v>
@@ -5548,7 +5547,7 @@
       <c r="F67" s="7"/>
       <c r="G67" s="5"/>
     </row>
-    <row r="68" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="62" t="s">
         <v>90</v>
       </c>
@@ -5559,12 +5558,12 @@
       <c r="F68" s="64"/>
       <c r="G68" s="65"/>
     </row>
-    <row r="69" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A69" s="54"/>
-      <c r="B69" s="89" t="s">
+      <c r="B69" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="90" t="s">
+      <c r="C69" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D69" s="61"/>
@@ -5572,7 +5571,7 @@
       <c r="F69" s="10"/>
       <c r="G69" s="5"/>
     </row>
-    <row r="70" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A70" s="54"/>
       <c r="B70" s="5" t="s">
         <v>93</v>
@@ -5583,7 +5582,7 @@
       <c r="F70" s="10"/>
       <c r="G70" s="5"/>
     </row>
-    <row r="71" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A71" s="54"/>
       <c r="B71" s="5" t="s">
         <v>94</v>
@@ -5596,6 +5595,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="G45:G46"/>
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="D1:G5"/>
     <mergeCell ref="A7:G7"/>
@@ -5612,73 +5626,54 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
   </mergeCells>
-  <conditionalFormatting sqref="C70:C1048576 C1:C26 C33:C35 C57:C68 C47:C52">
-    <cfRule type="duplicateValues" dxfId="54" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C57:C1048576 C33:C35 C1:C26 C47:C52">
-    <cfRule type="duplicateValues" dxfId="53" priority="16"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:C32">
-    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55:C56">
-    <cfRule type="duplicateValues" dxfId="51" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C55:C56">
-    <cfRule type="duplicateValues" dxfId="50" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C45:C46 C39:C40">
-    <cfRule type="duplicateValues" dxfId="49" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C53:C54">
-    <cfRule type="duplicateValues" dxfId="48" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C53:C54">
-    <cfRule type="duplicateValues" dxfId="47" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
-    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="duplicateValues" dxfId="46" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:C38">
     <cfRule type="duplicateValues" dxfId="45" priority="7"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C37">
+    <cfRule type="duplicateValues" dxfId="44" priority="8"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C38">
-    <cfRule type="duplicateValues" dxfId="44" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36">
-    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
+  <conditionalFormatting sqref="C39:C46">
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="6"/>
+  <conditionalFormatting sqref="C45:C46 C39:C40">
+    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C53:C54">
+    <cfRule type="duplicateValues" dxfId="40" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55:C56">
+    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C57:C1048576 C33:C35 C1:C26 C47:C52">
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C70:C1048576 C1:C26 C33:C35 C57:C68 C47:C52">
+    <cfRule type="duplicateValues" dxfId="35" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52 C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39:C46">
-    <cfRule type="duplicateValues" dxfId="36" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="67" max="6" man="1"/>
   </rowBreaks>
@@ -5696,67 +5691,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="6" width="17.25" style="68" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="69" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="6.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="6" width="17.28515625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-    </row>
-    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-    </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5765,23 +5760,23 @@
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -5795,52 +5790,52 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -5849,14 +5844,14 @@
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="134"/>
+      <c r="C13" s="96"/>
       <c r="D13" s="20" t="s">
         <v>6</v>
       </c>
@@ -5871,90 +5866,90 @@
       </c>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+    <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
       <c r="G14" s="107"/>
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="108"/>
       <c r="H15" s="25"/>
     </row>
-    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="108"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="108"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="108"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="109"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -5977,7 +5972,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -6000,7 +5995,7 @@
       <c r="G21" s="33"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -6023,7 +6018,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -6046,7 +6041,7 @@
       <c r="G23" s="33"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -6060,18 +6055,18 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -6083,12 +6078,12 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -6111,12 +6106,12 @@
       <c r="G26" s="33"/>
       <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -6133,12 +6128,12 @@
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -6153,12 +6148,12 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
         <v>11</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>101</v>
       </c>
@@ -6173,12 +6168,12 @@
       </c>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>56</v>
       </c>
@@ -6193,7 +6188,7 @@
       </c>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
@@ -6213,12 +6208,12 @@
       </c>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
       </c>
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="135" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="34" t="s">
@@ -6236,12 +6231,12 @@
       </c>
       <c r="H32" s="27"/>
     </row>
-    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
       </c>
-      <c r="B33" s="98"/>
+      <c r="B33" s="137"/>
       <c r="C33" s="34" t="s">
         <v>51</v>
       </c>
@@ -6257,7 +6252,7 @@
       </c>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
@@ -6278,7 +6273,7 @@
       <c r="G34" s="33"/>
       <c r="H34" s="27"/>
     </row>
-    <row r="35" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
@@ -6299,7 +6294,7 @@
       <c r="G35" s="33"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
@@ -6319,7 +6314,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
     </row>
-    <row r="37" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <f>IF(LEN(C37)=0,"",COUNTA($C$14:C37))</f>
         <v>19</v>
@@ -6337,7 +6332,7 @@
       <c r="F37" s="72"/>
       <c r="G37" s="27"/>
     </row>
-    <row r="38" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <f>IF(LEN(C38)=0,"",COUNTA($C$14:C38))</f>
         <v>20</v>
@@ -6361,18 +6356,18 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <f>IF(LEN(C39)=0,"",COUNTA($C$14:C39))</f>
         <v>21</v>
       </c>
-      <c r="B39" s="91" t="s">
+      <c r="B39" s="148" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="D39" s="103" t="s">
+      <c r="D39" s="150" t="s">
         <v>64</v>
       </c>
       <c r="E39" s="32">
@@ -6381,31 +6376,31 @@
       <c r="F39" s="32">
         <v>137000</v>
       </c>
-      <c r="G39" s="105" t="s">
+      <c r="G39" s="152" t="s">
         <v>65</v>
       </c>
       <c r="H39" s="39"/>
     </row>
-    <row r="40" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
         <f>IF(LEN(C40)=0,"",COUNTA($C$14:C40))</f>
         <v>22</v>
       </c>
-      <c r="B40" s="102"/>
+      <c r="B40" s="149"/>
       <c r="C40" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D40" s="104"/>
+      <c r="D40" s="151"/>
       <c r="E40" s="32">
         <v>137000</v>
       </c>
       <c r="F40" s="32">
         <v>137000</v>
       </c>
-      <c r="G40" s="106"/>
+      <c r="G40" s="153"/>
       <c r="H40" s="39"/>
     </row>
-    <row r="41" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
         <f>IF(LEN(C41)=0,"",COUNTA($C$14:C41))</f>
         <v>23</v>
@@ -6426,7 +6421,7 @@
       <c r="G41" s="33"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
         <f>IF(LEN(C42)=0,"",COUNTA($C$14:C42))</f>
         <v>24</v>
@@ -6445,7 +6440,7 @@
       <c r="G42" s="33"/>
       <c r="H42" s="27"/>
     </row>
-    <row r="43" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="28">
         <f>IF(LEN(C43)=0,"",COUNTA($C$14:C43))</f>
         <v>25</v>
@@ -6466,7 +6461,7 @@
       <c r="G43" s="33"/>
       <c r="H43" s="27"/>
     </row>
-    <row r="44" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A44" s="28">
         <f>IF(LEN(C44)=0,"",COUNTA($C$14:C44))</f>
         <v>26</v>
@@ -6485,7 +6480,7 @@
       <c r="G44" s="33"/>
       <c r="H44" s="27"/>
     </row>
-    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
         <f>IF(LEN(C45)=0,"",COUNTA($C$14:C45))</f>
         <v>27</v>
@@ -6504,7 +6499,7 @@
       <c r="G45" s="33"/>
       <c r="H45" s="27"/>
     </row>
-    <row r="46" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
         <f>IF(LEN(C46)=0,"",COUNTA($C$14:C46))</f>
         <v>28</v>
@@ -6523,7 +6518,7 @@
       <c r="G46" s="33"/>
       <c r="H46" s="27"/>
     </row>
-    <row r="47" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="28">
         <f>IF(LEN(C47)=0,"",COUNTA($C$14:C47))</f>
         <v>29</v>
@@ -6544,13 +6539,13 @@
       <c r="G47" s="33"/>
       <c r="H47" s="27"/>
     </row>
-    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="93" t="s">
+    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="94"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="95"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="106"/>
       <c r="E48" s="21">
         <f>SUM(E14:E47)</f>
         <v>2497000</v>
@@ -6562,7 +6557,7 @@
       <c r="G48" s="38"/>
       <c r="H48" s="27"/>
     </row>
-    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="50"/>
       <c r="B49" s="51"/>
       <c r="C49" s="50"/>
@@ -6571,73 +6566,73 @@
       <c r="F49" s="52"/>
       <c r="G49" s="53"/>
     </row>
-    <row r="50" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A50" s="96" t="s">
+    <row r="50" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="96"/>
-      <c r="C50" s="96"/>
-      <c r="D50" s="96"/>
+      <c r="B50" s="144"/>
+      <c r="C50" s="144"/>
+      <c r="D50" s="144"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="54"/>
     </row>
-    <row r="51" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="56"/>
-      <c r="B51" s="88" t="s">
+      <c r="B51" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C51" s="88"/>
-      <c r="D51" s="88"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="88"/>
-    </row>
-    <row r="52" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C51" s="93"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="93"/>
+      <c r="F51" s="93"/>
+      <c r="G51" s="93"/>
+    </row>
+    <row r="52" spans="1:7" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="56"/>
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="88"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
-    </row>
-    <row r="53" spans="1:7" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="93"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="93"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="93"/>
+    </row>
+    <row r="53" spans="1:7" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="57"/>
-      <c r="B53" s="88" t="s">
+      <c r="B53" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="88"/>
-      <c r="D53" s="88"/>
-      <c r="E53" s="88"/>
-      <c r="F53" s="88"/>
-      <c r="G53" s="88"/>
-    </row>
-    <row r="54" spans="1:7" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="93"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="93"/>
+      <c r="F53" s="93"/>
+      <c r="G53" s="93"/>
+    </row>
+    <row r="54" spans="1:7" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="59"/>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C54" s="87"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="87"/>
-      <c r="G54" s="87"/>
-    </row>
-    <row r="55" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="92"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="92"/>
+    </row>
+    <row r="55" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="54"/>
-      <c r="B55" s="88" t="s">
+      <c r="B55" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="88"/>
-      <c r="D55" s="88"/>
-      <c r="E55" s="88"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88"/>
-    </row>
-    <row r="56" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C55" s="93"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="93"/>
+      <c r="F55" s="93"/>
+      <c r="G55" s="93"/>
+    </row>
+    <row r="56" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="54"/>
       <c r="B56" s="57" t="s">
         <v>88</v>
@@ -6648,7 +6643,7 @@
       <c r="F56" s="7"/>
       <c r="G56" s="5"/>
     </row>
-    <row r="57" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A57" s="54"/>
       <c r="B57" s="57" t="s">
         <v>89</v>
@@ -6659,7 +6654,7 @@
       <c r="F57" s="7"/>
       <c r="G57" s="5"/>
     </row>
-    <row r="58" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A58" s="62" t="s">
         <v>90</v>
       </c>
@@ -6670,12 +6665,12 @@
       <c r="F58" s="64"/>
       <c r="G58" s="65"/>
     </row>
-    <row r="59" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="54"/>
-      <c r="B59" s="89" t="s">
+      <c r="B59" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C59" s="90" t="s">
+      <c r="C59" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D59" s="61"/>
@@ -6683,7 +6678,7 @@
       <c r="F59" s="10"/>
       <c r="G59" s="5"/>
     </row>
-    <row r="60" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="54"/>
       <c r="B60" s="5" t="s">
         <v>93</v>
@@ -6694,7 +6689,7 @@
       <c r="F60" s="10"/>
       <c r="G60" s="5"/>
     </row>
-    <row r="61" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="54"/>
       <c r="B61" s="5" t="s">
         <v>94</v>
@@ -6707,14 +6702,16 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="D1:G5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="D39:D40"/>
@@ -6725,59 +6722,55 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="B27:B30"/>
-    <mergeCell ref="D1:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A10:G11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
   </mergeCells>
-  <conditionalFormatting sqref="C60:C1048576 C1:C26 C32:C34 C47:C58 C41:C45">
-    <cfRule type="duplicateValues" dxfId="35" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C1048576 C32:C34 C1:C26 C41:C45">
-    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:C31">
-    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39:C40">
-    <cfRule type="duplicateValues" dxfId="32" priority="10"/>
+  <conditionalFormatting sqref="C35">
+    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
-    <cfRule type="duplicateValues" dxfId="31" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
+  <conditionalFormatting sqref="C35:C37">
+    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35:C37">
-    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37">
     <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+  <conditionalFormatting sqref="C38:C40">
+    <cfRule type="duplicateValues" dxfId="26" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+  <conditionalFormatting sqref="C39:C40">
+    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46">
+    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47:C1048576 C32:C34 C1:C26 C41:C45">
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C60:C1048576 C1:C26 C32:C34 C47:C58 C41:C45">
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45 C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C38:C40">
-    <cfRule type="duplicateValues" dxfId="22" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="57" max="6" man="1"/>
   </rowBreaks>
@@ -6795,67 +6788,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L65"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="6" width="17.25" style="68" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="69" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="6.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="6" width="17.28515625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-    </row>
-    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-    </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -6864,23 +6857,23 @@
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -6894,52 +6887,52 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -6948,14 +6941,14 @@
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="134"/>
+      <c r="C13" s="96"/>
       <c r="D13" s="20" t="s">
         <v>6</v>
       </c>
@@ -6970,90 +6963,90 @@
       </c>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+    <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
       <c r="G14" s="107"/>
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="108"/>
       <c r="H15" s="25"/>
     </row>
-    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="108"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="108"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="108"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="109"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -7076,7 +7069,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -7099,7 +7092,7 @@
       <c r="G21" s="33"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -7122,7 +7115,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -7145,7 +7138,7 @@
       <c r="G23" s="33"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -7159,18 +7152,18 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -7182,12 +7175,12 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -7210,12 +7203,12 @@
       <c r="G26" s="33"/>
       <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -7232,12 +7225,12 @@
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -7252,12 +7245,12 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
         <v>11</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>101</v>
       </c>
@@ -7272,12 +7265,12 @@
       </c>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>56</v>
       </c>
@@ -7292,7 +7285,7 @@
       </c>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
@@ -7312,12 +7305,12 @@
       </c>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
       </c>
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="135" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="34" t="s">
@@ -7335,12 +7328,12 @@
       </c>
       <c r="H32" s="27"/>
     </row>
-    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
       </c>
-      <c r="B33" s="98"/>
+      <c r="B33" s="137"/>
       <c r="C33" s="34" t="s">
         <v>51</v>
       </c>
@@ -7356,7 +7349,7 @@
       </c>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
@@ -7377,7 +7370,7 @@
       <c r="G34" s="33"/>
       <c r="H34" s="27"/>
     </row>
-    <row r="35" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
@@ -7398,7 +7391,7 @@
       <c r="G35" s="33"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" s="74" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
@@ -7418,7 +7411,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
     </row>
-    <row r="37" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" s="40" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <f>IF(LEN(C37)=0,"",COUNTA($C$14:C37))</f>
         <v>19</v>
@@ -7436,7 +7429,7 @@
       <c r="F37" s="72"/>
       <c r="G37" s="27"/>
     </row>
-    <row r="38" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <f>IF(LEN(C38)=0,"",COUNTA($C$14:C38))</f>
         <v>20</v>
@@ -7459,12 +7452,12 @@
       <c r="G38" s="33"/>
       <c r="H38" s="27"/>
     </row>
-    <row r="39" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="40" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <f>IF(LEN(C39)=0,"",COUNTA($C$34:C39))</f>
         <v>6</v>
       </c>
-      <c r="B39" s="99" t="s">
+      <c r="B39" s="145" t="s">
         <v>104</v>
       </c>
       <c r="C39" s="24" t="s">
@@ -7479,16 +7472,16 @@
       <c r="F39" s="45">
         <v>30000</v>
       </c>
-      <c r="G39" s="100" t="s">
+      <c r="G39" s="146" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="40" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="40" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
         <f>IF(LEN(C40)=0,"",COUNTA($C$34:C40))</f>
         <v>7</v>
       </c>
-      <c r="B40" s="99"/>
+      <c r="B40" s="145"/>
       <c r="C40" s="24" t="s">
         <v>108</v>
       </c>
@@ -7501,20 +7494,20 @@
       <c r="F40" s="45">
         <v>20000</v>
       </c>
-      <c r="G40" s="101"/>
-    </row>
-    <row r="41" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G40" s="147"/>
+    </row>
+    <row r="41" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
         <f>IF(LEN(C41)=0,"",COUNTA($C$14:C41))</f>
         <v>23</v>
       </c>
-      <c r="B41" s="91" t="s">
+      <c r="B41" s="148" t="s">
         <v>62</v>
       </c>
       <c r="C41" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="D41" s="103" t="s">
+      <c r="D41" s="150" t="s">
         <v>64</v>
       </c>
       <c r="E41" s="32">
@@ -7523,31 +7516,31 @@
       <c r="F41" s="32">
         <v>137000</v>
       </c>
-      <c r="G41" s="105" t="s">
+      <c r="G41" s="152" t="s">
         <v>65</v>
       </c>
       <c r="H41" s="39"/>
     </row>
-    <row r="42" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" s="40" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
         <f>IF(LEN(C42)=0,"",COUNTA($C$14:C42))</f>
         <v>24</v>
       </c>
-      <c r="B42" s="102"/>
+      <c r="B42" s="149"/>
       <c r="C42" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D42" s="104"/>
+      <c r="D42" s="151"/>
       <c r="E42" s="32">
         <v>137000</v>
       </c>
       <c r="F42" s="32">
         <v>137000</v>
       </c>
-      <c r="G42" s="106"/>
+      <c r="G42" s="153"/>
       <c r="H42" s="39"/>
     </row>
-    <row r="43" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A43" s="28">
         <f>IF(LEN(C43)=0,"",COUNTA($C$14:C43))</f>
         <v>25</v>
@@ -7568,7 +7561,7 @@
       <c r="G43" s="33"/>
       <c r="H43" s="27"/>
     </row>
-    <row r="44" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="28">
         <f>IF(LEN(C44)=0,"",COUNTA($C$14:C44))</f>
         <v>26</v>
@@ -7587,7 +7580,7 @@
       <c r="G44" s="33"/>
       <c r="H44" s="27"/>
     </row>
-    <row r="45" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
         <f>IF(LEN(C45)=0,"",COUNTA($C$14:C45))</f>
         <v>27</v>
@@ -7608,7 +7601,7 @@
       <c r="G45" s="33"/>
       <c r="H45" s="27"/>
     </row>
-    <row r="46" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
         <f>IF(LEN(C46)=0,"",COUNTA($C$14:C46))</f>
         <v>28</v>
@@ -7627,7 +7620,7 @@
       <c r="G46" s="33"/>
       <c r="H46" s="27"/>
     </row>
-    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="28">
         <f>IF(LEN(C47)=0,"",COUNTA($C$14:C47))</f>
         <v>29</v>
@@ -7646,7 +7639,7 @@
       <c r="G47" s="33"/>
       <c r="H47" s="27"/>
     </row>
-    <row r="48" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A48" s="28">
         <f>IF(LEN(C48)=0,"",COUNTA($C$14:C48))</f>
         <v>30</v>
@@ -7665,12 +7658,12 @@
       <c r="G48" s="33"/>
       <c r="H48" s="27"/>
     </row>
-    <row r="49" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="28">
         <f>IF(LEN(C49)=0,"",COUNTA($C$14:C49))</f>
         <v>31</v>
       </c>
-      <c r="B49" s="91" t="s">
+      <c r="B49" s="148" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="24" t="s">
@@ -7688,12 +7681,12 @@
       <c r="G49" s="33"/>
       <c r="H49" s="27"/>
     </row>
-    <row r="50" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A50" s="28">
         <f>IF(LEN(C50)=0,"",COUNTA($C$14:C50))</f>
         <v>32</v>
       </c>
-      <c r="B50" s="92"/>
+      <c r="B50" s="154"/>
       <c r="C50" s="24" t="s">
         <v>76</v>
       </c>
@@ -7709,7 +7702,7 @@
       <c r="G50" s="33"/>
       <c r="H50" s="27"/>
     </row>
-    <row r="51" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A51" s="28">
         <f>IF(LEN(C51)=0,"",COUNTA($C$14:C51))</f>
         <v>33</v>
@@ -7730,13 +7723,13 @@
       <c r="G51" s="33"/>
       <c r="H51" s="27"/>
     </row>
-    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="93" t="s">
+    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="94"/>
-      <c r="C52" s="94"/>
-      <c r="D52" s="95"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="105"/>
+      <c r="D52" s="106"/>
       <c r="E52" s="21">
         <f>SUM(E14:E51)</f>
         <v>3000000</v>
@@ -7748,7 +7741,7 @@
       <c r="G52" s="38"/>
       <c r="H52" s="27"/>
     </row>
-    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="50"/>
       <c r="B53" s="51"/>
       <c r="C53" s="50"/>
@@ -7757,73 +7750,73 @@
       <c r="F53" s="52"/>
       <c r="G53" s="53"/>
     </row>
-    <row r="54" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A54" s="96" t="s">
+    <row r="54" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
+      <c r="B54" s="144"/>
+      <c r="C54" s="144"/>
+      <c r="D54" s="144"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="54"/>
     </row>
-    <row r="55" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="56"/>
-      <c r="B55" s="88" t="s">
+      <c r="B55" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="88"/>
-      <c r="D55" s="88"/>
-      <c r="E55" s="88"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88"/>
-    </row>
-    <row r="56" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C55" s="93"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="93"/>
+      <c r="F55" s="93"/>
+      <c r="G55" s="93"/>
+    </row>
+    <row r="56" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="56"/>
-      <c r="B56" s="88" t="s">
+      <c r="B56" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="88"/>
-      <c r="D56" s="88"/>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
-    </row>
-    <row r="57" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="93"/>
+    </row>
+    <row r="57" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="57"/>
-      <c r="B57" s="88" t="s">
+      <c r="B57" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="88"/>
-      <c r="D57" s="88"/>
-      <c r="E57" s="88"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="88"/>
-    </row>
-    <row r="58" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="93"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="93"/>
+      <c r="F57" s="93"/>
+      <c r="G57" s="93"/>
+    </row>
+    <row r="58" spans="1:8" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="59"/>
-      <c r="B58" s="87" t="s">
+      <c r="B58" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="87"/>
-      <c r="D58" s="87"/>
-      <c r="E58" s="87"/>
-      <c r="F58" s="87"/>
-      <c r="G58" s="87"/>
-    </row>
-    <row r="59" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="92"/>
+      <c r="D58" s="92"/>
+      <c r="E58" s="92"/>
+      <c r="F58" s="92"/>
+      <c r="G58" s="92"/>
+    </row>
+    <row r="59" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="54"/>
-      <c r="B59" s="88" t="s">
+      <c r="B59" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="88"/>
-      <c r="D59" s="88"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88"/>
-    </row>
-    <row r="60" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="93"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="93"/>
+    </row>
+    <row r="60" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="54"/>
       <c r="B60" s="57" t="s">
         <v>88</v>
@@ -7834,7 +7827,7 @@
       <c r="F60" s="7"/>
       <c r="G60" s="5"/>
     </row>
-    <row r="61" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="54"/>
       <c r="B61" s="57" t="s">
         <v>89</v>
@@ -7845,7 +7838,7 @@
       <c r="F61" s="7"/>
       <c r="G61" s="5"/>
     </row>
-    <row r="62" spans="1:8" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="62" t="s">
         <v>90</v>
       </c>
@@ -7856,12 +7849,12 @@
       <c r="F62" s="64"/>
       <c r="G62" s="65"/>
     </row>
-    <row r="63" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A63" s="54"/>
-      <c r="B63" s="89" t="s">
+      <c r="B63" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="90" t="s">
+      <c r="C63" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D63" s="61"/>
@@ -7869,7 +7862,7 @@
       <c r="F63" s="10"/>
       <c r="G63" s="5"/>
     </row>
-    <row r="64" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A64" s="54"/>
       <c r="B64" s="5" t="s">
         <v>93</v>
@@ -7880,7 +7873,7 @@
       <c r="F64" s="10"/>
       <c r="G64" s="5"/>
     </row>
-    <row r="65" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="54"/>
       <c r="B65" s="5" t="s">
         <v>94</v>
@@ -7893,6 +7886,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="G39:G40"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="D1:G5"/>
     <mergeCell ref="A7:G7"/>
@@ -7909,70 +7917,51 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="B57:G57"/>
   </mergeCells>
-  <conditionalFormatting sqref="C64:C1048576 C1:C26 C32:C34 C51:C62 C43:C47">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27:C31">
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C35">
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C35:C37">
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37">
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:C42">
+    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:C42">
+    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C49:C50">
+    <cfRule type="duplicateValues" dxfId="8" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51:C1048576 C32:C34 C1:C26 C43:C47">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C31">
-    <cfRule type="duplicateValues" dxfId="19" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C49:C50">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C49:C50">
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41:C42">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C48">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C48">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C36">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35:C37">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  <conditionalFormatting sqref="C64:C1048576 C1:C26 C32:C34 C51:C62 C43:C47">
+    <cfRule type="duplicateValues" dxfId="5" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47 C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C38:C42">
-    <cfRule type="duplicateValues" dxfId="6" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="61" max="6" man="1"/>
   </rowBreaks>
@@ -7990,67 +7979,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L56"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.4140625" style="67" customWidth="1"/>
-    <col min="3" max="3" width="53.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.58203125" style="19" customWidth="1"/>
-    <col min="5" max="6" width="17.25" style="68" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="69" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="6.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="6" width="17.28515625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-    </row>
-    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-    </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -8059,23 +8048,23 @@
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="122" t="s">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -8089,52 +8078,52 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="130"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -8143,14 +8132,14 @@
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="93" t="s">
+      <c r="B13" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="95"/>
+      <c r="C13" s="106"/>
       <c r="D13" s="20" t="s">
         <v>6</v>
       </c>
@@ -8165,90 +8154,90 @@
       </c>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A14" s="135">
+    <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="132">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="138" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="97">
         <v>200000</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="97">
         <v>200000</v>
       </c>
       <c r="G14" s="107"/>
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="140"/>
+    <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="139"/>
       <c r="D15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="108"/>
       <c r="H15" s="25"/>
     </row>
-    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="140"/>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="139"/>
       <c r="D16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="108"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="140"/>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="108"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="140"/>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="133"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="108"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="137"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="141"/>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="134"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="109"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
@@ -8271,7 +8260,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
@@ -8294,7 +8283,7 @@
       <c r="G21" s="33"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
@@ -8317,7 +8306,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
@@ -8340,7 +8329,7 @@
       <c r="G23" s="33"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
@@ -8354,18 +8343,18 @@
       <c r="D24" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="111">
+      <c r="E24" s="100">
         <v>60000</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="100">
         <v>60000</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="111" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
@@ -8377,12 +8366,12 @@
       <c r="D25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="114"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
@@ -8405,12 +8394,12 @@
       <c r="G26" s="33"/>
       <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="113" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -8427,12 +8416,12 @@
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
@@ -8447,12 +8436,12 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
         <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
         <v>11</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="34" t="s">
         <v>101</v>
       </c>
@@ -8467,12 +8456,12 @@
       </c>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
         <v>12</v>
       </c>
-      <c r="B30" s="115"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="34" t="s">
         <v>56</v>
       </c>
@@ -8487,7 +8476,7 @@
       </c>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
         <v>13</v>
@@ -8507,12 +8496,12 @@
       </c>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
       </c>
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="135" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="34" t="s">
@@ -8530,12 +8519,12 @@
       </c>
       <c r="H32" s="27"/>
     </row>
-    <row r="33" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
       </c>
-      <c r="B33" s="98"/>
+      <c r="B33" s="137"/>
       <c r="C33" s="34" t="s">
         <v>51</v>
       </c>
@@ -8551,7 +8540,7 @@
       </c>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
@@ -8569,7 +8558,7 @@
       <c r="F34" s="72"/>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
@@ -8590,7 +8579,7 @@
       <c r="G35" s="33"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
@@ -8611,7 +8600,7 @@
       <c r="G36" s="33"/>
       <c r="H36" s="27"/>
     </row>
-    <row r="37" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <f>IF(LEN(C37)=0,"",COUNTA($C$14:C37))</f>
         <v>19</v>
@@ -8632,7 +8621,7 @@
       <c r="G37" s="33"/>
       <c r="H37" s="27"/>
     </row>
-    <row r="38" spans="1:8" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <f>IF(LEN(C38)=0,"",COUNTA($C$14:C38))</f>
         <v>20</v>
@@ -8653,7 +8642,7 @@
       <c r="G38" s="33"/>
       <c r="H38" s="27"/>
     </row>
-    <row r="39" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <f>IF(LEN(C39)=0,"",COUNTA($C$14:C39))</f>
         <v>21</v>
@@ -8672,7 +8661,7 @@
       <c r="G39" s="33"/>
       <c r="H39" s="27"/>
     </row>
-    <row r="40" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
         <f>IF(LEN(C40)=0,"",COUNTA($C$14:C40))</f>
         <v>22</v>
@@ -8693,7 +8682,7 @@
       <c r="G40" s="33"/>
       <c r="H40" s="27"/>
     </row>
-    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
         <f>IF(LEN(C41)=0,"",COUNTA($C$14:C41))</f>
         <v>23</v>
@@ -8712,7 +8701,7 @@
       <c r="G41" s="33"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
         <f>IF(LEN(C42)=0,"",COUNTA($C$14:C42))</f>
         <v>24</v>
@@ -8733,13 +8722,13 @@
       <c r="G42" s="33"/>
       <c r="H42" s="27"/>
     </row>
-    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="93" t="s">
+    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="94"/>
-      <c r="C43" s="94"/>
-      <c r="D43" s="95"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="106"/>
       <c r="E43" s="21">
         <f>SUM(E14:E41)</f>
         <v>2000000</v>
@@ -8751,7 +8740,7 @@
       <c r="G43" s="38"/>
       <c r="H43" s="27"/>
     </row>
-    <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
       <c r="B44" s="51"/>
       <c r="C44" s="50"/>
@@ -8760,73 +8749,73 @@
       <c r="F44" s="52"/>
       <c r="G44" s="53"/>
     </row>
-    <row r="45" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A45" s="96" t="s">
+    <row r="45" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="96"/>
-      <c r="C45" s="96"/>
-      <c r="D45" s="96"/>
+      <c r="B45" s="144"/>
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="54"/>
     </row>
-    <row r="46" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="56"/>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="88"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="88"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="88"/>
-    </row>
-    <row r="47" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="93"/>
+    </row>
+    <row r="47" spans="1:8" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="56"/>
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="88"/>
-      <c r="D47" s="88"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="88"/>
-      <c r="G47" s="88"/>
-    </row>
-    <row r="48" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="93"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="93"/>
+      <c r="G47" s="93"/>
+    </row>
+    <row r="48" spans="1:8" s="58" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="57"/>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88"/>
-    </row>
-    <row r="49" spans="1:7" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="93"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="93"/>
+      <c r="F48" s="93"/>
+      <c r="G48" s="93"/>
+    </row>
+    <row r="49" spans="1:7" s="60" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="59"/>
-      <c r="B49" s="87" t="s">
+      <c r="B49" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C49" s="87"/>
-      <c r="D49" s="87"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="87"/>
-    </row>
-    <row r="50" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="92"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="92"/>
+      <c r="G49" s="92"/>
+    </row>
+    <row r="50" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="54"/>
-      <c r="B50" s="88" t="s">
+      <c r="B50" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="88"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="88"/>
-    </row>
-    <row r="51" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C50" s="93"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="93"/>
+      <c r="F50" s="93"/>
+      <c r="G50" s="93"/>
+    </row>
+    <row r="51" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="54"/>
       <c r="B51" s="57" t="s">
         <v>88</v>
@@ -8837,7 +8826,7 @@
       <c r="F51" s="7"/>
       <c r="G51" s="5"/>
     </row>
-    <row r="52" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="54"/>
       <c r="B52" s="57" t="s">
         <v>89</v>
@@ -8848,7 +8837,7 @@
       <c r="F52" s="7"/>
       <c r="G52" s="5"/>
     </row>
-    <row r="53" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" s="66" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="62" t="s">
         <v>90</v>
       </c>
@@ -8859,12 +8848,12 @@
       <c r="F53" s="64"/>
       <c r="G53" s="65"/>
     </row>
-    <row r="54" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="54"/>
-      <c r="B54" s="89" t="s">
+      <c r="B54" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="90" t="s">
+      <c r="C54" s="95" t="s">
         <v>92</v>
       </c>
       <c r="D54" s="61"/>
@@ -8872,7 +8861,7 @@
       <c r="F54" s="10"/>
       <c r="G54" s="5"/>
     </row>
-    <row r="55" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="54"/>
       <c r="B55" s="5" t="s">
         <v>93</v>
@@ -8883,7 +8872,7 @@
       <c r="F55" s="10"/>
       <c r="G55" s="5"/>
     </row>
-    <row r="56" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="54"/>
       <c r="B56" s="5" t="s">
         <v>94</v>
@@ -8896,6 +8885,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="A43:D43"/>
@@ -8912,30 +8910,21 @@
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
   </mergeCells>
-  <conditionalFormatting sqref="C55:C1048576 C1:C26 C35:C53 C32:C33">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  <conditionalFormatting sqref="C27:C31">
+    <cfRule type="duplicateValues" dxfId="3" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:C1048576 C1:C26">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32:C1048576 C1:C26">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C31">
-    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
+  <conditionalFormatting sqref="C55:C1048576 C1:C26 C35:C53 C32:C33">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="52" max="6" man="1"/>
   </rowBreaks>
